--- a/ig/document/StructureDefinition-medcom-document-observation.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T10:37:57+00:00</t>
+    <t>2026-03-10T10:54:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3092,7 +3092,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>91</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>120</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>145</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>153</v>
       </c>
@@ -4644,7 +4644,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>181</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>212</v>
       </c>
@@ -5368,7 +5368,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>221</v>
       </c>
@@ -5966,7 +5966,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>262</v>
       </c>
@@ -6208,7 +6208,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>282</v>
       </c>
@@ -12606,7 +12606,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
         <v>422</v>
       </c>
@@ -13212,7 +13212,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>468</v>
       </c>
@@ -26488,12 +26488,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP196">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/ig/document/StructureDefinition-medcom-document-observation.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T10:54:08+00:00</t>
+    <t>2026-04-29T08:07:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
